--- a/Irish Competitions 2026 Bowling stats.xlsx
+++ b/Irish Competitions 2026 Bowling stats.xlsx
@@ -14,9 +14,6 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="Irish_Competitions_2026_Bowling_stats_up_to_end_of_May_2026" localSheetId="0">Sheet1!$A$1:$U$347</definedName>
-  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,40 +23,8 @@
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <connection id="1" name="Irish Competitions 2026 Bowling stats up to end of May 2026" type="6" refreshedVersion="6" background="1" saveData="1">
-    <textPr codePage="850" sourceFile="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Irish Cup &amp; National Cup matches-\Irish Competitions 2026 Bowling stats up to end of May 2026.csv" comma="1">
-      <textFields count="21">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="562">
   <si>
     <t>Group</t>
   </si>
@@ -1739,6 +1704,12 @@
   </si>
   <si>
     <t>Ross Waite</t>
+  </si>
+  <si>
+    <t>Leinster 1st XI v CSNI 1st XI, Rathmines - 19 July 2026</t>
+  </si>
+  <si>
+    <t>0-54</t>
   </si>
 </sst>
 </file>
@@ -1793,10 +1764,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Irish Competitions 2026 Bowling stats up to end of May 2026" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2062,7 +2029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U513"/>
+  <dimension ref="A1:U518"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
@@ -34245,6 +34212,325 @@
         <v>9.6</v>
       </c>
     </row>
+    <row r="514" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>560</v>
+      </c>
+      <c r="B514" t="s">
+        <v>277</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+      <c r="D514">
+        <v>1</v>
+      </c>
+      <c r="E514">
+        <v>9</v>
+      </c>
+      <c r="F514">
+        <v>1</v>
+      </c>
+      <c r="G514">
+        <v>50</v>
+      </c>
+      <c r="H514">
+        <v>1</v>
+      </c>
+      <c r="I514">
+        <v>50</v>
+      </c>
+      <c r="J514">
+        <v>5.56</v>
+      </c>
+      <c r="K514">
+        <v>0</v>
+      </c>
+      <c r="L514">
+        <v>0</v>
+      </c>
+      <c r="M514" s="1">
+        <v>18264</v>
+      </c>
+      <c r="N514" s="1">
+        <v>18264</v>
+      </c>
+      <c r="O514">
+        <v>54</v>
+      </c>
+      <c r="P514">
+        <v>39</v>
+      </c>
+      <c r="Q514">
+        <v>7</v>
+      </c>
+      <c r="R514">
+        <v>1</v>
+      </c>
+      <c r="S514" t="s">
+        <v>449</v>
+      </c>
+      <c r="T514" t="s">
+        <v>24</v>
+      </c>
+      <c r="U514">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="515" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>560</v>
+      </c>
+      <c r="B515" t="s">
+        <v>278</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+      <c r="D515">
+        <v>1</v>
+      </c>
+      <c r="E515">
+        <v>7.3</v>
+      </c>
+      <c r="F515">
+        <v>0</v>
+      </c>
+      <c r="G515">
+        <v>54</v>
+      </c>
+      <c r="H515">
+        <v>0</v>
+      </c>
+      <c r="J515">
+        <v>7.2</v>
+      </c>
+      <c r="K515">
+        <v>0</v>
+      </c>
+      <c r="L515">
+        <v>0</v>
+      </c>
+      <c r="M515" t="s">
+        <v>561</v>
+      </c>
+      <c r="N515" t="s">
+        <v>561</v>
+      </c>
+      <c r="O515">
+        <v>45</v>
+      </c>
+      <c r="P515">
+        <v>21</v>
+      </c>
+      <c r="Q515">
+        <v>6</v>
+      </c>
+      <c r="R515">
+        <v>2</v>
+      </c>
+      <c r="S515" t="s">
+        <v>24</v>
+      </c>
+      <c r="T515" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="516" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>560</v>
+      </c>
+      <c r="B516" t="s">
+        <v>359</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
+      <c r="E516">
+        <v>10</v>
+      </c>
+      <c r="F516">
+        <v>0</v>
+      </c>
+      <c r="G516">
+        <v>37</v>
+      </c>
+      <c r="H516">
+        <v>5</v>
+      </c>
+      <c r="I516">
+        <v>7.4</v>
+      </c>
+      <c r="J516">
+        <v>3.7</v>
+      </c>
+      <c r="K516">
+        <v>1</v>
+      </c>
+      <c r="L516">
+        <v>0</v>
+      </c>
+      <c r="M516" s="1">
+        <v>13636</v>
+      </c>
+      <c r="N516" s="1">
+        <v>13636</v>
+      </c>
+      <c r="O516">
+        <v>60</v>
+      </c>
+      <c r="P516">
+        <v>44</v>
+      </c>
+      <c r="Q516">
+        <v>4</v>
+      </c>
+      <c r="R516">
+        <v>0</v>
+      </c>
+      <c r="S516" t="s">
+        <v>122</v>
+      </c>
+      <c r="T516" t="s">
+        <v>31</v>
+      </c>
+      <c r="U516">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="517" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>560</v>
+      </c>
+      <c r="B517" t="s">
+        <v>283</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+      <c r="D517">
+        <v>1</v>
+      </c>
+      <c r="E517">
+        <v>9</v>
+      </c>
+      <c r="F517">
+        <v>0</v>
+      </c>
+      <c r="G517">
+        <v>59</v>
+      </c>
+      <c r="H517">
+        <v>1</v>
+      </c>
+      <c r="I517">
+        <v>59</v>
+      </c>
+      <c r="J517">
+        <v>6.56</v>
+      </c>
+      <c r="K517">
+        <v>0</v>
+      </c>
+      <c r="L517">
+        <v>0</v>
+      </c>
+      <c r="M517" s="1">
+        <v>21551</v>
+      </c>
+      <c r="N517" s="1">
+        <v>21551</v>
+      </c>
+      <c r="O517">
+        <v>54</v>
+      </c>
+      <c r="P517">
+        <v>27</v>
+      </c>
+      <c r="Q517">
+        <v>9</v>
+      </c>
+      <c r="R517">
+        <v>0</v>
+      </c>
+      <c r="S517" t="s">
+        <v>23</v>
+      </c>
+      <c r="T517" t="s">
+        <v>24</v>
+      </c>
+      <c r="U517">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="518" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>560</v>
+      </c>
+      <c r="B518" t="s">
+        <v>287</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+      <c r="D518">
+        <v>1</v>
+      </c>
+      <c r="E518">
+        <v>10</v>
+      </c>
+      <c r="F518">
+        <v>0</v>
+      </c>
+      <c r="G518">
+        <v>40</v>
+      </c>
+      <c r="H518">
+        <v>1</v>
+      </c>
+      <c r="I518">
+        <v>40</v>
+      </c>
+      <c r="J518">
+        <v>4</v>
+      </c>
+      <c r="K518">
+        <v>0</v>
+      </c>
+      <c r="L518">
+        <v>0</v>
+      </c>
+      <c r="M518" s="1">
+        <v>14611</v>
+      </c>
+      <c r="N518" s="1">
+        <v>14611</v>
+      </c>
+      <c r="O518">
+        <v>60</v>
+      </c>
+      <c r="P518">
+        <v>30</v>
+      </c>
+      <c r="Q518">
+        <v>2</v>
+      </c>
+      <c r="R518">
+        <v>0</v>
+      </c>
+      <c r="S518" t="s">
+        <v>31</v>
+      </c>
+      <c r="T518" t="s">
+        <v>24</v>
+      </c>
+      <c r="U518">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Irish Competitions 2026 Bowling stats.xlsx
+++ b/Irish Competitions 2026 Bowling stats.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2463" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="564">
   <si>
     <t>Group</t>
   </si>
@@ -1710,6 +1710,12 @@
   </si>
   <si>
     <t>0-54</t>
+  </si>
+  <si>
+    <t>Muckamore 2nd XI v Brigade 2nd XI, Moylena - 9 August 2026</t>
+  </si>
+  <si>
+    <t>Sam Gordon</t>
   </si>
 </sst>
 </file>
@@ -2029,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U518"/>
+  <dimension ref="A1:U524"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
@@ -34531,6 +34537,390 @@
         <v>60</v>
       </c>
     </row>
+    <row r="519" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>562</v>
+      </c>
+      <c r="B519" t="s">
+        <v>235</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+      <c r="D519">
+        <v>1</v>
+      </c>
+      <c r="E519">
+        <v>3</v>
+      </c>
+      <c r="F519">
+        <v>0</v>
+      </c>
+      <c r="G519">
+        <v>23</v>
+      </c>
+      <c r="H519">
+        <v>0</v>
+      </c>
+      <c r="J519">
+        <v>7.67</v>
+      </c>
+      <c r="K519">
+        <v>0</v>
+      </c>
+      <c r="L519">
+        <v>0</v>
+      </c>
+      <c r="M519" t="s">
+        <v>344</v>
+      </c>
+      <c r="N519" t="s">
+        <v>344</v>
+      </c>
+      <c r="O519">
+        <v>18</v>
+      </c>
+      <c r="P519">
+        <v>8</v>
+      </c>
+      <c r="Q519">
+        <v>1</v>
+      </c>
+      <c r="R519">
+        <v>1</v>
+      </c>
+      <c r="S519" t="s">
+        <v>187</v>
+      </c>
+      <c r="T519" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="520" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>562</v>
+      </c>
+      <c r="B520" t="s">
+        <v>238</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+      <c r="D520">
+        <v>1</v>
+      </c>
+      <c r="E520">
+        <v>4</v>
+      </c>
+      <c r="F520">
+        <v>0</v>
+      </c>
+      <c r="G520">
+        <v>24</v>
+      </c>
+      <c r="H520">
+        <v>2</v>
+      </c>
+      <c r="I520">
+        <v>12</v>
+      </c>
+      <c r="J520">
+        <v>6</v>
+      </c>
+      <c r="K520">
+        <v>0</v>
+      </c>
+      <c r="L520">
+        <v>0</v>
+      </c>
+      <c r="M520" s="1">
+        <v>45323</v>
+      </c>
+      <c r="N520" s="1">
+        <v>45323</v>
+      </c>
+      <c r="O520">
+        <v>24</v>
+      </c>
+      <c r="P520">
+        <v>12</v>
+      </c>
+      <c r="Q520">
+        <v>2</v>
+      </c>
+      <c r="R520">
+        <v>0</v>
+      </c>
+      <c r="S520" t="s">
+        <v>57</v>
+      </c>
+      <c r="T520" t="s">
+        <v>24</v>
+      </c>
+      <c r="U520">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="521" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>562</v>
+      </c>
+      <c r="B521" t="s">
+        <v>563</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521">
+        <v>1</v>
+      </c>
+      <c r="E521">
+        <v>2.4</v>
+      </c>
+      <c r="F521">
+        <v>0</v>
+      </c>
+      <c r="G521">
+        <v>14</v>
+      </c>
+      <c r="H521">
+        <v>1</v>
+      </c>
+      <c r="I521">
+        <v>14</v>
+      </c>
+      <c r="J521">
+        <v>5.25</v>
+      </c>
+      <c r="K521">
+        <v>0</v>
+      </c>
+      <c r="L521">
+        <v>0</v>
+      </c>
+      <c r="M521" s="1">
+        <v>41640</v>
+      </c>
+      <c r="N521" s="1">
+        <v>41640</v>
+      </c>
+      <c r="O521">
+        <v>16</v>
+      </c>
+      <c r="P521">
+        <v>8</v>
+      </c>
+      <c r="Q521">
+        <v>1</v>
+      </c>
+      <c r="R521">
+        <v>0</v>
+      </c>
+      <c r="S521" t="s">
+        <v>31</v>
+      </c>
+      <c r="T521" t="s">
+        <v>24</v>
+      </c>
+      <c r="U521">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="522" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>562</v>
+      </c>
+      <c r="B522" t="s">
+        <v>358</v>
+      </c>
+      <c r="C522">
+        <v>1</v>
+      </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
+      <c r="E522">
+        <v>4</v>
+      </c>
+      <c r="F522">
+        <v>0</v>
+      </c>
+      <c r="G522">
+        <v>34</v>
+      </c>
+      <c r="H522">
+        <v>1</v>
+      </c>
+      <c r="I522">
+        <v>34</v>
+      </c>
+      <c r="J522">
+        <v>8.5</v>
+      </c>
+      <c r="K522">
+        <v>0</v>
+      </c>
+      <c r="L522">
+        <v>0</v>
+      </c>
+      <c r="M522" s="1">
+        <v>12420</v>
+      </c>
+      <c r="N522" s="1">
+        <v>12420</v>
+      </c>
+      <c r="O522">
+        <v>24</v>
+      </c>
+      <c r="P522">
+        <v>10</v>
+      </c>
+      <c r="Q522">
+        <v>2</v>
+      </c>
+      <c r="R522">
+        <v>2</v>
+      </c>
+      <c r="S522" t="s">
+        <v>31</v>
+      </c>
+      <c r="T522" t="s">
+        <v>24</v>
+      </c>
+      <c r="U522">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="523" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>562</v>
+      </c>
+      <c r="B523" t="s">
+        <v>489</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+      <c r="D523">
+        <v>1</v>
+      </c>
+      <c r="E523">
+        <v>4</v>
+      </c>
+      <c r="F523">
+        <v>0</v>
+      </c>
+      <c r="G523">
+        <v>12</v>
+      </c>
+      <c r="H523">
+        <v>2</v>
+      </c>
+      <c r="I523">
+        <v>6</v>
+      </c>
+      <c r="J523">
+        <v>3</v>
+      </c>
+      <c r="K523">
+        <v>0</v>
+      </c>
+      <c r="L523">
+        <v>0</v>
+      </c>
+      <c r="M523" s="2">
+        <v>46358</v>
+      </c>
+      <c r="N523" s="2">
+        <v>46358</v>
+      </c>
+      <c r="O523">
+        <v>24</v>
+      </c>
+      <c r="P523">
+        <v>15</v>
+      </c>
+      <c r="Q523">
+        <v>0</v>
+      </c>
+      <c r="R523">
+        <v>0</v>
+      </c>
+      <c r="S523" t="s">
+        <v>31</v>
+      </c>
+      <c r="T523" t="s">
+        <v>24</v>
+      </c>
+      <c r="U523">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="524" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>562</v>
+      </c>
+      <c r="B524" t="s">
+        <v>435</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+      <c r="D524">
+        <v>1</v>
+      </c>
+      <c r="E524">
+        <v>2</v>
+      </c>
+      <c r="F524">
+        <v>0</v>
+      </c>
+      <c r="G524">
+        <v>11</v>
+      </c>
+      <c r="H524">
+        <v>2</v>
+      </c>
+      <c r="I524">
+        <v>5.5</v>
+      </c>
+      <c r="J524">
+        <v>5.5</v>
+      </c>
+      <c r="K524">
+        <v>0</v>
+      </c>
+      <c r="L524">
+        <v>0</v>
+      </c>
+      <c r="M524" s="2">
+        <v>46328</v>
+      </c>
+      <c r="N524" s="2">
+        <v>46328</v>
+      </c>
+      <c r="O524">
+        <v>12</v>
+      </c>
+      <c r="P524">
+        <v>5</v>
+      </c>
+      <c r="Q524">
+        <v>1</v>
+      </c>
+      <c r="R524">
+        <v>0</v>
+      </c>
+      <c r="S524" t="s">
+        <v>24</v>
+      </c>
+      <c r="T524" t="s">
+        <v>24</v>
+      </c>
+      <c r="U524">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Irish Competitions 2026 Bowling stats.xlsx
+++ b/Irish Competitions 2026 Bowling stats.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Irish Cup &amp; National Cup &amp; Ulster Plate matches-\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED358618-6A37-4F15-83E7-EC8454027BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21075" windowHeight="13650"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2489" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="566">
   <si>
     <t>Group</t>
   </si>
@@ -1716,12 +1717,18 @@
   </si>
   <si>
     <t>Sam Gordon</t>
+  </si>
+  <si>
+    <t>CSNI 1st XI v Pembroke 1st XI, Castle Avenue - 16 August 2026</t>
+  </si>
+  <si>
+    <t>0-76</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2034,8 +2041,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U524"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U529"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.5703125" bestFit="1" customWidth="1"/>
@@ -34921,6 +34928,319 @@
         <v>6</v>
       </c>
     </row>
+    <row r="525" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>564</v>
+      </c>
+      <c r="B525" t="s">
+        <v>277</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+      <c r="D525">
+        <v>1</v>
+      </c>
+      <c r="E525">
+        <v>10</v>
+      </c>
+      <c r="F525">
+        <v>0</v>
+      </c>
+      <c r="G525">
+        <v>76</v>
+      </c>
+      <c r="H525">
+        <v>0</v>
+      </c>
+      <c r="J525">
+        <v>7.6</v>
+      </c>
+      <c r="K525">
+        <v>0</v>
+      </c>
+      <c r="L525">
+        <v>0</v>
+      </c>
+      <c r="M525" t="s">
+        <v>565</v>
+      </c>
+      <c r="N525" t="s">
+        <v>565</v>
+      </c>
+      <c r="O525">
+        <v>60</v>
+      </c>
+      <c r="P525">
+        <v>28</v>
+      </c>
+      <c r="Q525">
+        <v>13</v>
+      </c>
+      <c r="R525">
+        <v>0</v>
+      </c>
+      <c r="S525" t="s">
+        <v>46</v>
+      </c>
+      <c r="T525" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="526" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>564</v>
+      </c>
+      <c r="B526" t="s">
+        <v>278</v>
+      </c>
+      <c r="C526">
+        <v>1</v>
+      </c>
+      <c r="D526">
+        <v>1</v>
+      </c>
+      <c r="E526">
+        <v>10</v>
+      </c>
+      <c r="F526">
+        <v>0</v>
+      </c>
+      <c r="G526">
+        <v>69</v>
+      </c>
+      <c r="H526">
+        <v>1</v>
+      </c>
+      <c r="I526">
+        <v>69</v>
+      </c>
+      <c r="J526">
+        <v>6.9</v>
+      </c>
+      <c r="K526">
+        <v>0</v>
+      </c>
+      <c r="L526">
+        <v>0</v>
+      </c>
+      <c r="M526" s="1">
+        <v>25204</v>
+      </c>
+      <c r="N526" s="1">
+        <v>25204</v>
+      </c>
+      <c r="O526">
+        <v>60</v>
+      </c>
+      <c r="P526">
+        <v>13</v>
+      </c>
+      <c r="Q526">
+        <v>6</v>
+      </c>
+      <c r="R526">
+        <v>0</v>
+      </c>
+      <c r="S526" t="s">
+        <v>24</v>
+      </c>
+      <c r="T526" t="s">
+        <v>24</v>
+      </c>
+      <c r="U526">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="527" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>564</v>
+      </c>
+      <c r="B527" t="s">
+        <v>359</v>
+      </c>
+      <c r="C527">
+        <v>1</v>
+      </c>
+      <c r="D527">
+        <v>1</v>
+      </c>
+      <c r="E527">
+        <v>10</v>
+      </c>
+      <c r="F527">
+        <v>0</v>
+      </c>
+      <c r="G527">
+        <v>85</v>
+      </c>
+      <c r="H527">
+        <v>2</v>
+      </c>
+      <c r="I527">
+        <v>42.5</v>
+      </c>
+      <c r="J527">
+        <v>8.5</v>
+      </c>
+      <c r="K527">
+        <v>0</v>
+      </c>
+      <c r="L527">
+        <v>0</v>
+      </c>
+      <c r="M527" s="1">
+        <v>31079</v>
+      </c>
+      <c r="N527" s="1">
+        <v>31079</v>
+      </c>
+      <c r="O527">
+        <v>60</v>
+      </c>
+      <c r="P527">
+        <v>24</v>
+      </c>
+      <c r="Q527">
+        <v>11</v>
+      </c>
+      <c r="R527">
+        <v>1</v>
+      </c>
+      <c r="S527" t="s">
+        <v>351</v>
+      </c>
+      <c r="T527" t="s">
+        <v>24</v>
+      </c>
+      <c r="U527">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="528" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>564</v>
+      </c>
+      <c r="B528" t="s">
+        <v>283</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+      <c r="D528">
+        <v>1</v>
+      </c>
+      <c r="E528">
+        <v>10</v>
+      </c>
+      <c r="F528">
+        <v>1</v>
+      </c>
+      <c r="G528">
+        <v>30</v>
+      </c>
+      <c r="H528">
+        <v>0</v>
+      </c>
+      <c r="J528">
+        <v>3</v>
+      </c>
+      <c r="K528">
+        <v>0</v>
+      </c>
+      <c r="L528">
+        <v>0</v>
+      </c>
+      <c r="M528" t="s">
+        <v>45</v>
+      </c>
+      <c r="N528" t="s">
+        <v>45</v>
+      </c>
+      <c r="O528">
+        <v>60</v>
+      </c>
+      <c r="P528">
+        <v>41</v>
+      </c>
+      <c r="Q528">
+        <v>3</v>
+      </c>
+      <c r="R528">
+        <v>0</v>
+      </c>
+      <c r="S528" t="s">
+        <v>23</v>
+      </c>
+      <c r="T528" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="529" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>564</v>
+      </c>
+      <c r="B529" t="s">
+        <v>287</v>
+      </c>
+      <c r="C529">
+        <v>1</v>
+      </c>
+      <c r="D529">
+        <v>1</v>
+      </c>
+      <c r="E529">
+        <v>10</v>
+      </c>
+      <c r="F529">
+        <v>0</v>
+      </c>
+      <c r="G529">
+        <v>45</v>
+      </c>
+      <c r="H529">
+        <v>4</v>
+      </c>
+      <c r="I529">
+        <v>11.25</v>
+      </c>
+      <c r="J529">
+        <v>4.5</v>
+      </c>
+      <c r="K529">
+        <v>0</v>
+      </c>
+      <c r="L529">
+        <v>0</v>
+      </c>
+      <c r="M529" s="1">
+        <v>53053</v>
+      </c>
+      <c r="N529" s="1">
+        <v>53053</v>
+      </c>
+      <c r="O529">
+        <v>60</v>
+      </c>
+      <c r="P529">
+        <v>28</v>
+      </c>
+      <c r="Q529">
+        <v>2</v>
+      </c>
+      <c r="R529">
+        <v>0</v>
+      </c>
+      <c r="S529" t="s">
+        <v>46</v>
+      </c>
+      <c r="T529" t="s">
+        <v>24</v>
+      </c>
+      <c r="U529">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Irish Competitions 2026 Bowling stats.xlsx
+++ b/Irish Competitions 2026 Bowling stats.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +24,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,12 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,114 +428,138 @@
   </sheetPr>
   <dimension ref="A1:V622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="78" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="26" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="38" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="10" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="10" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="15" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="28" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="24" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="28" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="25" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="10" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="10" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="10" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="10" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="10" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="10" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="13" bestFit="1" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Bowler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Bowler ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Innings</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Overs</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Maidens</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Runs Per Over</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Five Wickets in an Innings</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Ten Wickets in a Match</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Best Bowling in an Innings</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Best Bowling in a Match</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Balls</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Dots</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Fours</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Sixes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wides</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>No Balls</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Strike Rate</t>
         </is>
